--- a/erp-server/erp-server-oms/src/main/resources/excel/kolFeedbackCostTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolFeedbackCostTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22560" windowHeight="11120"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -45,6 +52,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">* </t>
     </r>
     <r>
@@ -74,7 +88,19 @@
     </r>
   </si>
   <si>
-    <t>金额（原币）</t>
+    <r>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>金额（原币）</t>
+    </r>
   </si>
   <si>
     <t>备注</t>
@@ -700,14 +726,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1236,10 +1259,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="4" width="17.1818181818182" customWidth="1"/>
-    <col min="5" max="5" width="18.9090909090909" customWidth="1"/>
+    <col min="1" max="4" width="17.1833333333333" customWidth="1"/>
+    <col min="5" max="5" width="18.9083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1252,7 +1275,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
